--- a/output/pdf_financials_xlsx/FPC.xlsx
+++ b/output/pdf_financials_xlsx/FPC.xlsx
@@ -5315,10 +5315,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.039487</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.039487</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>1.131283</v>
@@ -18942,7 +18942,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FPC.xlsx
+++ b/output/pdf_financials_xlsx/FPC.xlsx
@@ -981,37 +981,37 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004127</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.024325</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.268858</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.425092</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.091734</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.070826</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.053128</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.271355</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.383838</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.263575</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.10976</v>
       </c>
     </row>
     <row r="13">
@@ -1835,37 +1835,37 @@
         <v>-2.922457</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.006007</v>
+        <v>-6.010134</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.360014</v>
+        <v>-2.384339</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.23217</v>
+        <v>-4.501028</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.84125</v>
+        <v>-4.266342</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-8.764258</v>
+        <v>-8.855992000000001</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.44469</v>
+        <v>-4.515516</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.871652</v>
+        <v>-3.92478</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.166572</v>
+        <v>-3.437927</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.993122</v>
+        <v>-3.37696</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.341039</v>
+        <v>-3.604614</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.772662</v>
+        <v>-1.882422</v>
       </c>
     </row>
     <row r="28">
@@ -1939,37 +1939,37 @@
         <v>-2.878692</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.957677</v>
+        <v>-5.961804</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.349349</v>
+        <v>-2.373674</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.219409</v>
+        <v>-4.488267</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.828489</v>
+        <v>-4.253581</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-8.747526000000001</v>
+        <v>-8.839259999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.408252</v>
+        <v>-4.479078</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.837845</v>
+        <v>-3.890973</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.145508</v>
+        <v>-3.416863</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.977273</v>
+        <v>-3.361111</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.310493</v>
+        <v>-3.574068</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.743176</v>
+        <v>-1.852936</v>
       </c>
     </row>
     <row r="30">
@@ -2220,16 +2220,16 @@
         <v>9.389505</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>53.39514</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>8.932271</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.11575</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.630751</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>4.149395</v>
@@ -2324,16 +2324,16 @@
         <v>9.389505</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>53.39514</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>8.932271</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.11575</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.630751</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>4.149395</v>
@@ -2948,16 +2948,16 @@
         <v>0.104713</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>53.469657</v>
+        <v>0.074517</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>9.347925</v>
+        <v>0.415654</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.278906</v>
+        <v>0.163156</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.832895</v>
+        <v>0.202144</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.256291</v>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -36987,7 +36987,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -37062,7 +37062,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -38695,7 +38695,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -39227,7 +39227,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -40483,7 +40483,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -41927,7 +41927,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">

--- a/output/pdf_financials_xlsx/FPC.xlsx
+++ b/output/pdf_financials_xlsx/FPC.xlsx
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.001038</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -31176,7 +31176,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -32359,7 +32363,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
